--- a/exports/LAURUSLABS_full_report.xlsx
+++ b/exports/LAURUSLABS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.91</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>499.5</v>
+        <v>488.5</v>
       </c>
       <c r="I2" t="n">
         <v>494.3408879999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.47</v>
+        <v>-6.57</v>
       </c>
       <c r="L2" t="n">
-        <v>6.28</v>
+        <v>6.6</v>
       </c>
       <c r="M2" t="n">
         <v>1.58</v>
       </c>
       <c r="N2" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="O2" t="n">
         <v>-0.8100000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>6.98</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44589.55208333334</v>
+        <v>44592.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>497.8</v>
+        <v>506.55</v>
       </c>
       <c r="I3" t="n">
         <v>499.5855299461099</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.9</v>
+        <v>-3.69</v>
       </c>
       <c r="L3" t="n">
-        <v>3.53</v>
+        <v>5.79</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="N3" t="n">
         <v>7.71</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>11.03</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>532.5</v>
+        <v>506.75</v>
       </c>
       <c r="I4" t="n">
         <v>512.6908341810278</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>5.12</v>
+        <v>0.04</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="N4" t="n">
-        <v>3.98</v>
+        <v>6.16</v>
       </c>
       <c r="O4" t="n">
         <v>1.04</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44623.38541666666</v>
+        <v>44623.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>535.25</v>
+        <v>544</v>
       </c>
       <c r="I5" t="n">
         <v>541.8575516572704</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.62</v>
+        <v>-7.35</v>
       </c>
       <c r="L5" t="n">
         <v>7.84</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.02</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44677.38541666666</v>
+        <v>44677.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>588.35</v>
+        <v>573.85</v>
       </c>
       <c r="I6" t="n">
         <v>584.1898022139578</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>53.83333333333334</v>
+        <v>54</v>
       </c>
       <c r="K6" t="n">
-        <v>8.15</v>
+        <v>5.49</v>
       </c>
       <c r="L6" t="n">
         <v>4.15</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.53</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44701.55208333334</v>
+        <v>44704.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>573.55</v>
+        <v>576.95</v>
       </c>
       <c r="I7" t="n">
         <v>575.4971557649599</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05</v>
+        <v>-0.54</v>
       </c>
       <c r="L7" t="n">
         <v>4.89</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>6.92</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>546.05</v>
+        <v>530.35</v>
       </c>
       <c r="I8" t="n">
         <v>538.7258728787649</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.36</v>
+        <v>-8.08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.48</v>
+        <v>8.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.25</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>3.53</v>
       </c>
       <c r="O8" t="n">
         <v>-0.1</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.19</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>470</v>
+        <v>492.65</v>
       </c>
       <c r="I9" t="n">
         <v>486.5103606274864</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>11.38</v>
+        <v>7.11</v>
       </c>
       <c r="L9" t="n">
         <v>2.28</v>
@@ -954,7 +1061,7 @@
         <v>2.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>4.47</v>
       </c>
       <c r="O9" t="n">
         <v>-3.53</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.89</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44767.55208333334</v>
+        <v>44768.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>496.6</v>
+        <v>490.7</v>
       </c>
       <c r="I10" t="n">
         <v>492.9191658971912</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="L10" t="n">
         <v>4.6</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.17</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44769.38541666666</v>
+        <v>44769.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>495.2</v>
+        <v>515.9</v>
       </c>
       <c r="I11" t="n">
         <v>512.6146375854239</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.92</v>
+        <v>-5.14</v>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>5.44</v>
       </c>
       <c r="M11" t="n">
         <v>0.5600000000000001</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.23</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44806.55208333334</v>
+        <v>44809.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>568.8</v>
+        <v>563.35</v>
       </c>
       <c r="I12" t="n">
         <v>563.9444359456057</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>37</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>10.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>4.13</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.76</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44852.55208333334</v>
+        <v>44853.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>511.45</v>
+        <v>526.3</v>
       </c>
       <c r="I13" t="n">
         <v>525.4948147613587</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K13" t="n">
-        <v>9.210000000000001</v>
+        <v>6.58</v>
       </c>
       <c r="L13" t="n">
         <v>2.42</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>7.15</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44855.38541666666</v>
+        <v>44855.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>517.9</v>
+        <v>476.1</v>
       </c>
       <c r="I14" t="n">
         <v>499.0832855633899</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.6</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>2.86</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-0</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.85</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>311.35</v>
+        <v>321.8</v>
       </c>
       <c r="I15" t="n">
         <v>321.7246446086548</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>133</v>
+        <v>135.8333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>34.6</v>
+        <v>32.41</v>
       </c>
       <c r="L15" t="n">
         <v>8.91</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.5</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>306.25</v>
+        <v>304.5</v>
       </c>
       <c r="I16" t="n">
         <v>305.6014531722615</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.83</v>
+        <v>-5.38</v>
       </c>
       <c r="L16" t="n">
-        <v>5.84</v>
+        <v>6.22</v>
       </c>
       <c r="M16" t="n">
         <v>0.11</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.23</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>305.15</v>
+        <v>306.15</v>
       </c>
       <c r="I17" t="n">
         <v>305.8174554406472</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.21</v>
+        <v>-0.54</v>
       </c>
       <c r="L17" t="n">
         <v>2.07</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45037.55208333334</v>
+        <v>45040.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>303</v>
+        <v>299.75</v>
       </c>
       <c r="I18" t="n">
         <v>301.3088377596649</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.03</v>
+        <v>-2.09</v>
       </c>
       <c r="L18" t="n">
-        <v>2.06</v>
+        <v>4.02</v>
       </c>
       <c r="M18" t="n">
         <v>0.1</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.63</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45048.55208333334</v>
+        <v>45049.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>312</v>
+        <v>317.05</v>
       </c>
       <c r="I19" t="n">
         <v>313.982861582333</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.09</v>
+        <v>-5.77</v>
       </c>
       <c r="L19" t="n">
         <v>6.06</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45056.55208333334</v>
+        <v>45057.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>332.95</v>
+        <v>309.65</v>
       </c>
       <c r="I20" t="n">
         <v>310.4169684314936</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>5.01</v>
+        <v>-2.33</v>
       </c>
       <c r="L20" t="n">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="M20" t="n">
         <v>0.09</v>
       </c>
       <c r="N20" t="n">
-        <v>0.92</v>
+        <v>3.68</v>
       </c>
       <c r="O20" t="n">
         <v>3.19</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.69</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45069.55208333334</v>
+        <v>45070.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="I21" t="n">
         <v>330.8800061940274</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.73</v>
+        <v>-7.22</v>
       </c>
       <c r="L21" t="n">
         <v>8.06</v>
@@ -1638,7 +1889,7 @@
         <v>0.51</v>
       </c>
       <c r="N21" t="n">
-        <v>1.43</v>
+        <v>6.29</v>
       </c>
       <c r="O21" t="n">
         <v>-3.68</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.99</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45111.55208333334</v>
+        <v>45112.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>351.05</v>
+        <v>348.6</v>
       </c>
       <c r="I22" t="n">
         <v>349.2936638839847</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K22" t="n">
-        <v>5.74</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
         <v>5.39</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.48</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45112.55208333334</v>
+        <v>45113.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>355.5</v>
+        <v>368</v>
       </c>
       <c r="I23" t="n">
         <v>367.7159977870008</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.98</v>
+        <v>-5.57</v>
       </c>
       <c r="L23" t="n">
-        <v>2.01</v>
+        <v>6.14</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="N23" t="n">
-        <v>1.27</v>
+        <v>2.81</v>
       </c>
       <c r="O23" t="n">
         <v>1.27</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>7.88</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45132.55208333334</v>
+        <v>45133.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>346.3</v>
+        <v>342.2</v>
       </c>
       <c r="I24" t="n">
         <v>346.1344788519487</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.9</v>
+        <v>-7.01</v>
       </c>
       <c r="L24" t="n">
-        <v>6.62</v>
+        <v>7.61</v>
       </c>
       <c r="M24" t="n">
         <v>0.43</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>5.54</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>357.4</v>
+        <v>362.8</v>
       </c>
       <c r="I25" t="n">
         <v>358.0939181441598</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.44</v>
+        <v>-6.02</v>
       </c>
       <c r="L25" t="n">
-        <v>5.06</v>
+        <v>7.54</v>
       </c>
       <c r="M25" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="N25" t="n">
         <v>4.34</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>7.56</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45149.55208333334</v>
+        <v>45152.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>388.8</v>
+        <v>384.2</v>
       </c>
       <c r="I26" t="n">
         <v>385.5171861058093</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>7.17</v>
+        <v>5.9</v>
       </c>
       <c r="L26" t="n">
         <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="N26" t="n">
         <v>2.68</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7.18</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45174.38541666666</v>
+        <v>45174.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>401.65</v>
+        <v>406.9</v>
       </c>
       <c r="I27" t="n">
         <v>404.5403001181314</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.54</v>
+        <v>-5.91</v>
       </c>
       <c r="L27" t="n">
-        <v>5.58</v>
+        <v>6.96</v>
       </c>
       <c r="M27" t="n">
         <v>1.06</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>5.52</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="I28" t="n">
         <v>392.0455711707006</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>0.02</v>
+        <v>-5.87</v>
       </c>
       <c r="L28" t="n">
-        <v>1.52</v>
+        <v>7.29</v>
       </c>
       <c r="M28" t="n">
-        <v>-0</v>
+        <v>1.74</v>
       </c>
       <c r="N28" t="n">
-        <v>0.75</v>
+        <v>5.65</v>
       </c>
       <c r="O28" t="n">
         <v>3.01</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.9</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45266.55208333334</v>
+        <v>45267.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>379</v>
+        <v>389.5</v>
       </c>
       <c r="I29" t="n">
         <v>381.1683784608771</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>85.16666666666667</v>
+        <v>86</v>
       </c>
       <c r="K29" t="n">
-        <v>1.04</v>
+        <v>-1.7</v>
       </c>
       <c r="L29" t="n">
         <v>7.42</v>
@@ -2094,7 +2441,7 @@
         <v>1.69</v>
       </c>
       <c r="N29" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
         <v>-5.65</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.24</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45310.55208333334</v>
+        <v>45311.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="I30" t="n">
         <v>409.5589851839587</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K30" t="n">
-        <v>5.78</v>
+        <v>3.21</v>
       </c>
       <c r="L30" t="n">
         <v>4.21</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.62</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45338.55208333334</v>
+        <v>45341.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>400</v>
+        <v>408.85</v>
       </c>
       <c r="I31" t="n">
         <v>402.4938090775747</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5</v>
+        <v>-1.7</v>
       </c>
       <c r="L31" t="n">
         <v>3.02</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.56</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>411.1</v>
+        <v>400.65</v>
       </c>
       <c r="I32" t="n">
         <v>403.4318805604007</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K32" t="n">
-        <v>0.55</v>
+        <v>-2.01</v>
       </c>
       <c r="L32" t="n">
         <v>3.97</v>
@@ -2265,7 +2648,7 @@
         <v>0.84</v>
       </c>
       <c r="N32" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="O32" t="n">
         <v>1.72</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45383.55208333334</v>
+        <v>45384.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>405.85</v>
+        <v>415.05</v>
       </c>
       <c r="I33" t="n">
         <v>406.3501747798061</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.3</v>
+        <v>-3.59</v>
       </c>
       <c r="L33" t="n">
         <v>4.38</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.8</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45401.38541666666</v>
+        <v>45401.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>428.35</v>
+        <v>426</v>
       </c>
       <c r="I34" t="n">
         <v>426.3437519943399</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="L34" t="n">
         <v>2.42</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>7.86</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45433.55208333334</v>
+        <v>45434.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>453</v>
+        <v>457.6</v>
       </c>
       <c r="I35" t="n">
         <v>456.1987810210592</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>32</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.34</v>
+        <v>-7.42</v>
       </c>
       <c r="L35" t="n">
-        <v>7.37</v>
+        <v>8.09</v>
       </c>
       <c r="M35" t="n">
         <v>1.88</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.64</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>441.55</v>
+        <v>433.5</v>
       </c>
       <c r="I36" t="n">
         <v>433.6935057780936</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.51</v>
+        <v>-5.27</v>
       </c>
       <c r="L36" t="n">
         <v>5.92</v>
@@ -2493,7 +2924,7 @@
         <v>0.84</v>
       </c>
       <c r="N36" t="n">
-        <v>2.23</v>
+        <v>2.84</v>
       </c>
       <c r="O36" t="n">
         <v>0.78</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>6.14</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45476.55208333334</v>
+        <v>45477.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>436.45</v>
+        <v>458</v>
       </c>
       <c r="I37" t="n">
         <v>442.248084510547</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.68</v>
+        <v>-5.65</v>
       </c>
       <c r="L37" t="n">
-        <v>3.19</v>
+        <v>6.22</v>
       </c>
       <c r="M37" t="n">
         <v>1.38</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.49</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>457.4</v>
+        <v>445.65</v>
       </c>
       <c r="I38" t="n">
         <v>449.2646825589983</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.13</v>
+        <v>-2.7</v>
       </c>
       <c r="L38" t="n">
         <v>4.79</v>
@@ -2607,7 +3062,7 @@
         <v>0.26</v>
       </c>
       <c r="N38" t="n">
-        <v>2.14</v>
+        <v>3.67</v>
       </c>
       <c r="O38" t="n">
         <v>4.25</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>7.03</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45502.55208333334</v>
+        <v>45503.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>450</v>
+        <v>460.35</v>
       </c>
       <c r="I39" t="n">
         <v>458.0562195917873</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.98</v>
+        <v>-3.3</v>
       </c>
       <c r="L39" t="n">
-        <v>2.86</v>
+        <v>4.16</v>
       </c>
       <c r="M39" t="n">
         <v>0.33</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>9.18</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45509.38541666666</v>
+        <v>45509.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>433.95</v>
+        <v>430</v>
       </c>
       <c r="I40" t="n">
         <v>431.6634695660084</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-5.73</v>
+        <v>-6.59</v>
       </c>
       <c r="L40" t="n">
-        <v>6.38</v>
+        <v>7.22</v>
       </c>
       <c r="M40" t="n">
         <v>1.66</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.19</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45530.55208333334</v>
+        <v>45531.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>448</v>
+        <v>452.65</v>
       </c>
       <c r="I41" t="n">
         <v>449.7219716563256</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.19</v>
+        <v>-5.27</v>
       </c>
       <c r="L41" t="n">
-        <v>5.52</v>
+        <v>6.55</v>
       </c>
       <c r="M41" t="n">
         <v>1.38</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.11</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>485.75</v>
+        <v>462.85</v>
       </c>
       <c r="I42" t="n">
         <v>479.1419168909432</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K42" t="n">
-        <v>7.31</v>
+        <v>2.25</v>
       </c>
       <c r="L42" t="n">
         <v>1.4</v>
@@ -2835,7 +3338,7 @@
         <v>0.61</v>
       </c>
       <c r="N42" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O42" t="n">
         <v>1.27</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.65</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45575.38541666666</v>
+        <v>45575.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>461.65</v>
+        <v>466</v>
       </c>
       <c r="I43" t="n">
         <v>463.3724794287179</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>0.26</v>
+        <v>-0.68</v>
       </c>
       <c r="L43" t="n">
         <v>6.06</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.93</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45588.38541666666</v>
+        <v>45588.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>460.65</v>
+        <v>450.65</v>
       </c>
       <c r="I44" t="n">
         <v>452.7630452983195</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.15</v>
+        <v>-3.29</v>
       </c>
       <c r="L44" t="n">
         <v>4.72</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>8.93</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45590.55208333334</v>
+        <v>45593.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>463.65</v>
+        <v>493.05</v>
       </c>
       <c r="I45" t="n">
         <v>483.5202178016467</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.88</v>
+        <v>-9.41</v>
       </c>
       <c r="L45" t="n">
-        <v>6.2</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>0.02</v>
       </c>
       <c r="N45" t="n">
-        <v>2.83</v>
+        <v>6.65</v>
       </c>
       <c r="O45" t="n">
         <v>-0.65</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>13.26</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>567</v>
+        <v>558.5</v>
       </c>
       <c r="I46" t="n">
         <v>560.5399257350646</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>15</v>
+        <v>13.27</v>
       </c>
       <c r="L46" t="n">
         <v>6.79</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>5.46</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45653.55208333334</v>
+        <v>45656.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>587.3</v>
+        <v>590.45</v>
       </c>
       <c r="I47" t="n">
         <v>589.0169701813892</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.16</v>
+        <v>-5.72</v>
       </c>
       <c r="L47" t="n">
-        <v>5.72</v>
+        <v>6.65</v>
       </c>
       <c r="M47" t="n">
         <v>0.73</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>5.11</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45667.38541666666</v>
+        <v>45667.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>585.75</v>
+        <v>583.2</v>
       </c>
       <c r="I48" t="n">
         <v>583.8805574119875</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.8</v>
+        <v>-1.23</v>
       </c>
       <c r="L48" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="M48" t="n">
         <v>0.41</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>6.27</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45681.38541666666</v>
+        <v>45681.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>583.7</v>
+        <v>612.6</v>
       </c>
       <c r="I49" t="n">
         <v>593.768405100249</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.09</v>
+        <v>-5.04</v>
       </c>
       <c r="L49" t="n">
-        <v>1.71</v>
+        <v>5.05</v>
       </c>
       <c r="M49" t="n">
         <v>1.25</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>10.26</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>612.6</v>
+        <v>530.1</v>
       </c>
       <c r="I50" t="n">
         <v>549.7231882156933</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>-13.47</v>
       </c>
       <c r="L50" t="n">
-        <v>5.28</v>
+        <v>18.19</v>
       </c>
       <c r="M50" t="n">
-        <v>-0</v>
+        <v>0.42</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>12.91</v>
       </c>
       <c r="O50" t="n">
         <v>4.54</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>19.05</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>552.95</v>
+        <v>591.65</v>
       </c>
       <c r="I51" t="n">
         <v>584.9885262116836</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.31</v>
+        <v>-11.61</v>
       </c>
       <c r="L51" t="n">
         <v>15.07</v>
       </c>
       <c r="M51" t="n">
-        <v>0.63</v>
+        <v>2.35</v>
       </c>
       <c r="N51" t="n">
         <v>8.039999999999999</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>15.37</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45701.55208333334</v>
+        <v>45702.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>599.35</v>
+        <v>544.2</v>
       </c>
       <c r="I52" t="n">
         <v>594.4023573675283</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K52" t="n">
-        <v>1.3</v>
+        <v>-8.02</v>
       </c>
       <c r="L52" t="n">
-        <v>5.79</v>
+        <v>8.33</v>
       </c>
       <c r="M52" t="n">
         <v>0.66</v>
       </c>
       <c r="N52" t="n">
-        <v>2.89</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O52" t="n">
         <v>5.8</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>16.94</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>567.2</v>
+        <v>577.85</v>
       </c>
       <c r="I53" t="n">
         <v>571.3533702168758</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.23</v>
+        <v>-6.18</v>
       </c>
       <c r="L53" t="n">
         <v>10.99</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.18</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>619.4</v>
+        <v>569.45</v>
       </c>
       <c r="I54" t="n">
         <v>590.8861284733844</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K54" t="n">
-        <v>7.19</v>
+        <v>-1.45</v>
       </c>
       <c r="L54" t="n">
         <v>4.47</v>
@@ -3519,7 +4166,7 @@
         <v>1.54</v>
       </c>
       <c r="N54" t="n">
-        <v>2.13</v>
+        <v>7.02</v>
       </c>
       <c r="O54" t="n">
         <v>1.82</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>13.64</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>563.55</v>
+        <v>603.85</v>
       </c>
       <c r="I55" t="n">
         <v>603.3112259485655</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>1.04</v>
+        <v>-6.04</v>
       </c>
       <c r="L55" t="n">
         <v>9.19</v>
       </c>
       <c r="M55" t="n">
-        <v>3.02</v>
+        <v>3.81</v>
       </c>
       <c r="N55" t="n">
-        <v>3.18</v>
+        <v>7.75</v>
       </c>
       <c r="O55" t="n">
         <v>-7.02</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>13.35</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45777.38541666666</v>
+        <v>45777.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>612</v>
+        <v>601.1</v>
       </c>
       <c r="I56" t="n">
         <v>609.6173119037007</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>1.35</v>
+        <v>-0.46</v>
       </c>
       <c r="L56" t="n">
         <v>4.46</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.6</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45811.38541666666</v>
+        <v>45811.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>616.95</v>
+        <v>620</v>
       </c>
       <c r="I57" t="n">
         <v>619.2961420113188</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.64</v>
+        <v>-3.14</v>
       </c>
       <c r="L57" t="n">
         <v>4.81</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.12</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45827.55208333334</v>
+        <v>45828.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>646.35</v>
+        <v>641.7</v>
       </c>
       <c r="I58" t="n">
         <v>644.7479862267094</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="L58" t="n">
         <v>1.51</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.24</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>681.15</v>
+        <v>691.95</v>
       </c>
       <c r="I59" t="n">
         <v>681.7457259665222</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.15</v>
+        <v>-7.83</v>
       </c>
       <c r="L59" t="n">
-        <v>6.84</v>
+        <v>7.96</v>
       </c>
       <c r="M59" t="n">
         <v>0.75</v>
       </c>
       <c r="N59" t="n">
-        <v>2.14</v>
+        <v>3.35</v>
       </c>
       <c r="O59" t="n">
         <v>1.03</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.74</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45870.38541666666</v>
+        <v>45870.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>858.3</v>
+        <v>851.3</v>
       </c>
       <c r="I60" t="n">
         <v>853.755416000272</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>24.04</v>
+        <v>23.03</v>
       </c>
       <c r="L60" t="n">
         <v>1.91</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.5</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45887.55208333334</v>
+        <v>45888.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>868.75</v>
+        <v>879.35</v>
       </c>
       <c r="I61" t="n">
         <v>870.0609986700923</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.05</v>
+        <v>-3.29</v>
       </c>
       <c r="L61" t="n">
-        <v>3.24</v>
+        <v>3.37</v>
       </c>
       <c r="M61" t="n">
         <v>0.9399999999999999</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>6.03</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>900</v>
+        <v>831.4</v>
       </c>
       <c r="I62" t="n">
         <v>891.5912415226122</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K62" t="n">
-        <v>2.35</v>
+        <v>-5.45</v>
       </c>
       <c r="L62" t="n">
-        <v>3.29</v>
+        <v>6.4</v>
       </c>
       <c r="M62" t="n">
-        <v>0.73</v>
+        <v>2.19</v>
       </c>
       <c r="N62" t="n">
-        <v>2.91</v>
+        <v>7.52</v>
       </c>
       <c r="O62" t="n">
         <v>2.04</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>10.32</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45947.38541666666</v>
+        <v>45947.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>885.15</v>
+        <v>901</v>
       </c>
       <c r="I63" t="n">
         <v>893.5226944271863</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.46</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>7.51</v>
+        <v>8.49</v>
       </c>
       <c r="M63" t="n">
         <v>1.28</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.93</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45986.38541666666</v>
+        <v>45986.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>979.95</v>
+        <v>975</v>
       </c>
       <c r="I64" t="n">
         <v>978.0208741254933</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K64" t="n">
-        <v>8.76</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L64" t="n">
         <v>1.99</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>4.34</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1006</v>
+        <v>1026.1</v>
       </c>
       <c r="I65" t="n">
         <v>1017.274555745368</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.18</v>
+        <v>-5.24</v>
       </c>
       <c r="L65" t="n">
-        <v>3.78</v>
+        <v>5.76</v>
       </c>
       <c r="M65" t="n">
         <v>0.62</v>
       </c>
       <c r="N65" t="n">
-        <v>2.13</v>
+        <v>2.63</v>
       </c>
       <c r="O65" t="n">
         <v>-0.8</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.47</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1084.4</v>
+        <v>1039.9</v>
       </c>
       <c r="I66" t="n">
         <v>1082.2680037085</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K66" t="n">
-        <v>5.68</v>
+        <v>1.34</v>
       </c>
       <c r="L66" t="n">
         <v>3.92</v>
@@ -4203,7 +4994,7 @@
         <v>0.7</v>
       </c>
       <c r="N66" t="n">
-        <v>2.24</v>
+        <v>4.01</v>
       </c>
       <c r="O66" t="n">
         <v>2.63</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>7.78</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46070.55208333334</v>
+        <v>46071.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1011</v>
+        <v>1030.85</v>
       </c>
       <c r="I67" t="n">
         <v>1018.154560974138</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K67" t="n">
-        <v>2.78</v>
+        <v>0.87</v>
       </c>
       <c r="L67" t="n">
         <v>5.67</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.46</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1068</v>
+        <v>1030.6</v>
       </c>
       <c r="I68" t="n">
         <v>1031.34058106429</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>3.6</v>
+        <v>-0.02</v>
       </c>
       <c r="L68" t="n">
         <v>3.29</v>
@@ -4317,7 +5132,7 @@
         <v>3.91</v>
       </c>
       <c r="N68" t="n">
-        <v>2.19</v>
+        <v>3.45</v>
       </c>
       <c r="O68" t="n">
         <v>2.74</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>8.17</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>992</v>
+        <v>1023.2</v>
       </c>
       <c r="I69" t="n">
         <v>1019.694184873006</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K69" t="n">
-        <v>3.75</v>
+        <v>0.72</v>
       </c>
       <c r="L69" t="n">
         <v>3.63</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>8.4</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46188.55208333334</v>
+        <v>46189.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1391</v>
+        <v>1345.9</v>
       </c>
       <c r="I70" t="n">
         <v>1381.142638311868</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>82.16666666666667</v>
+        <v>83</v>
       </c>
       <c r="K70" t="n">
-        <v>35.95</v>
+        <v>31.54</v>
       </c>
       <c r="L70" t="n">
         <v>3.76</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>8.15</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46195.55208333334</v>
+        <v>46196.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1437.4</v>
+        <v>1466</v>
       </c>
       <c r="I71" t="n">
         <v>1443.204188853642</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.8</v>
+        <v>-8.92</v>
       </c>
       <c r="L71" t="n">
-        <v>7.07</v>
+        <v>10.41</v>
       </c>
       <c r="M71" t="n">
         <v>0.63</v>
       </c>
       <c r="N71" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O71" t="n">
         <v>-1</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.11</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46210.55208333334</v>
+        <v>46211.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>1474</v>
+        <v>1455</v>
       </c>
       <c r="I72" t="n">
         <v>1461.699672863294</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K72" t="n">
-        <v>0.55</v>
+        <v>-0.75</v>
       </c>
       <c r="L72" t="n">
         <v>2.11</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>7.38</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46213.55208333334</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1535.5</v>
+        <v>1552.2</v>
       </c>
       <c r="I73" t="n">
         <v>1551.595369353858</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.53</v>
+        <v>-6.68</v>
       </c>
       <c r="L73" t="n">
-        <v>6.39</v>
+        <v>7.01</v>
       </c>
       <c r="M73" t="n">
         <v>0.46</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>6.74</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46248.38541666666</v>
+        <v>46248.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>1810</v>
+        <v>1787.8</v>
       </c>
       <c r="I74" t="n">
         <v>1789.734148100159</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K74" t="n">
-        <v>16.61</v>
+        <v>15.18</v>
       </c>
       <c r="L74" t="n">
         <v>2.05</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>4.68</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>1862.1</v>
+        <v>1894.4</v>
       </c>
       <c r="I75" t="n">
         <v>1865.916810961807</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K75" t="n">
-        <v>-4.16</v>
+        <v>-5.96</v>
       </c>
       <c r="L75" t="n">
-        <v>4.56</v>
+        <v>6</v>
       </c>
       <c r="M75" t="n">
         <v>0.75</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>5.09</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46265.55208333334</v>
+        <v>46266.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>1862.8</v>
+        <v>1843</v>
       </c>
       <c r="I76" t="n">
         <v>1854.882029311555</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.67</v>
+        <v>-2.71</v>
       </c>
       <c r="L76" t="n">
-        <v>2.46</v>
+        <v>3.01</v>
       </c>
       <c r="M76" t="n">
         <v>0.04</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>6.63</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46272.55208333334</v>
+        <v>46273.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>1867.4</v>
+        <v>1947</v>
       </c>
       <c r="I77" t="n">
         <v>1928.806624214529</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K77" t="n">
-        <v>-1.32</v>
+        <v>-5.64</v>
       </c>
       <c r="L77" t="n">
-        <v>2.82</v>
+        <v>5.69</v>
       </c>
       <c r="M77" t="n">
         <v>1.4</v>
       </c>
       <c r="N77" t="n">
-        <v>1.36</v>
+        <v>4.05</v>
       </c>
       <c r="O77" t="n">
         <v>-0.31</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>7.42</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46280.55208333334</v>
+        <v>46281.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>1920.6</v>
+        <v>1882.5</v>
       </c>
       <c r="I78" t="n">
         <v>1884.462045719321</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K78" t="n">
-        <v>-1.36</v>
+        <v>-3.31</v>
       </c>
       <c r="L78" t="n">
         <v>4.33</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>6.76</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46283.55208333334</v>
+        <v>46286.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>1973.8</v>
+        <v>2014.8</v>
       </c>
       <c r="I79" t="n">
         <v>1999.241861803553</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K79" t="n">
-        <v>-4.85</v>
+        <v>-7.03</v>
       </c>
       <c r="L79" t="n">
-        <v>5.29</v>
+        <v>7.22</v>
       </c>
       <c r="M79" t="n">
         <v>0.21</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>6.38</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>2002</v>
+        <v>1944.4</v>
       </c>
       <c r="I80" t="n">
         <v>1972.554071697113</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.64</v>
+        <v>-3.49</v>
       </c>
       <c r="L80" t="n">
-        <v>3.11</v>
+        <v>4.04</v>
       </c>
       <c r="M80" t="n">
         <v>0.8100000000000001</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,25 +6008,25 @@
         <v>7.58</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H81" t="n">
-        <v>2052</v>
+        <v>2120.5</v>
       </c>
       <c r="I81" t="n">
         <v>2073.498697133215</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K81" t="n">
-        <v>-5.53</v>
+        <v>-9.06</v>
       </c>
       <c r="L81" t="n">
-        <v>5.84</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M81" t="n">
-        <v>0.26</v>
+        <v>1.12</v>
       </c>
       <c r="N81" t="n">
         <v>4.96</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5118,6 +6101,12 @@
       <c r="Q82" t="n">
         <v>2</v>
       </c>
+      <c r="R82" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7220,7 +8209,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.8</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="6">
@@ -7230,7 +8219,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="7">
@@ -7240,7 +8229,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>135.8</v>
       </c>
     </row>
     <row r="8">
@@ -7250,7 +8239,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7260,7 +8249,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.4</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="10">
@@ -7270,7 +8259,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="11">
@@ -7310,7 +8299,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.35</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="15">
@@ -7320,7 +8309,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.69</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -7330,7 +8319,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.99</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="17">
@@ -7340,7 +8329,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35.95</v>
+        <v>32.41</v>
       </c>
     </row>
     <row r="18">
@@ -7350,7 +8339,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -7360,7 +8349,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.6</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="20">
@@ -7370,7 +8359,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.42</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="21">
@@ -7380,7 +8369,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.07</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="22">
@@ -7390,7 +8379,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -7400,7 +8389,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -7410,7 +8399,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="25">
@@ -7430,7 +8419,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.25</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="27">
@@ -7440,7 +8429,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.140000000000001</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="28">
@@ -7450,7 +8439,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
